--- a/03_Outputs/all/01_TablasDescriptivas/idx4_Capacidad_vr.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx4_Capacidad_vr.xlsx
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.9823952680375323</v>
+        <v>0.9823952680375331</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -419,7 +419,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.6199261877189381</v>
+        <v>0.6199261877189384</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>2.380073812281062</v>
+        <v>2.380073812281063</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>3.000000000000001</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>46.58928480811765</v>
+        <v>46.58928480811764</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>32.74650893458441</v>
+        <v>32.74650893458443</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>46.58928480811765</v>
+        <v>46.58928480811764</v>
       </c>
       <c r="C11">
         <v>1</v>
